--- a/reports/hazop_system_27.xlsx
+++ b/reports/hazop_system_27.xlsx
@@ -479,7 +479,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HAZOP preparation — System 27</t>
+          <t>HAZOP preparation — System 27 (functional loops)</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>27-PT4250A, 27-PT4250A, 27-PT4250B, 27-PT4250B</t>
+          <t>27-PT4250A, 27-PT4250B</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -609,7 +609,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>27-PIC4803, 27-PT4803, 27-PT4803, 27-PV4803, 27-PY4803</t>
+          <t>27-PIC4803, 27-PT4803, 27-PV4803, 27-PY4803</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>27-PI4804, 27-PT4804, 27-PT4804</t>
+          <t>27-PI4804, 27-PT4804</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>27-PI4805, 27-PT4805, 27-PT4805</t>
+          <t>27-PI4805, 27-PT4805</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -690,7 +690,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>27-TI4806, 27-TT4806, 27-TT4806</t>
+          <t>27-TI4806, 27-TT4806</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>27-PDI4812, 27-PDT4812, 27-PDT4812</t>
+          <t>27-PDI4812, 27-PDT4812</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>27-HS4813, 27-XV4813, 27-XV4813, 27-XY4813, 27-ZL4813, 27-ZS4813</t>
+          <t>27-HS4813, 27-XV4813, 27-XY4813, 27-ZL4813, 27-ZS4813</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>27-HS4814, 27-XV4814, 27-XV4814, 27-XY4814, 27-ZL4814, 27-ZS4814</t>
+          <t>27-HS4814, 27-XV4814, 27-XY4814, 27-ZL4814, 27-ZS4814</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>27-PIC4825A, 27-PIC4825A, 27-PIC4825B, 27-PIC4825B, 27-PIC4825C, 27-PIC4825C, 27-PT4825, 27-PT4825</t>
+          <t>27-PIC4825A, 27-PIC4825B, 27-PIC4825C, 27-PT4825</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>27-HS4826, 27-XV4826, 27-XV4826, 27-XY4826, 27-ZL4826, 27-ZS4826</t>
+          <t>27-HS4826, 27-XV4826, 27-XY4826, 27-ZL4826, 27-ZS4826</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -933,7 +933,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>27-HS4828, 27-XV4828, 27-XV4828, 27-XY4828, 27-ZL4828, 27-ZS4828</t>
+          <t>27-HS4828, 27-XV4828, 27-XY4828, 27-ZL4828, 27-ZS4828</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -970,16 +970,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1019,15 +1022,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1056,7 +1074,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1085,7 +1106,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1114,7 +1138,10 @@
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1143,7 +1170,10 @@
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1160,16 +1190,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1182,7 +1215,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-PDI4812, 27-PDT4812, 27-PDT4812</t>
+          <t>Members: 27-PDI4812, 27-PDT4812</t>
         </is>
       </c>
     </row>
@@ -1209,15 +1242,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1246,7 +1294,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1275,7 +1326,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1292,16 +1346,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1314,7 +1371,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-HS4813, 27-XV4813, 27-XV4813, 27-XY4813, 27-ZL4813, 27-ZS4813</t>
+          <t>Members: 27-HS4813, 27-XV4813, 27-XY4813, 27-ZL4813, 27-ZS4813</t>
         </is>
       </c>
     </row>
@@ -1341,15 +1398,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1373,12 +1445,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>27-XV4813</t>
+          <t>27-XV4813 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1402,12 +1477,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>27-XV4813</t>
+          <t>27-XV4813 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1431,12 +1509,15 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>27-XV4813</t>
+          <t>27-XV4813 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1460,12 +1541,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>27-XV4813</t>
+          <t>27-XV4813 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1482,16 +1566,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1504,7 +1591,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-HS4814, 27-XV4814, 27-XV4814, 27-XY4814, 27-ZL4814, 27-ZS4814</t>
+          <t>Members: 27-HS4814, 27-XV4814, 27-XY4814, 27-ZL4814, 27-ZS4814</t>
         </is>
       </c>
     </row>
@@ -1531,15 +1618,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1563,12 +1665,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>27-XV4814</t>
+          <t>27-XV4814 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1592,12 +1697,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>27-XV4814</t>
+          <t>27-XV4814 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1621,12 +1729,15 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>27-XV4814</t>
+          <t>27-XV4814 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1650,12 +1761,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>27-XV4814</t>
+          <t>27-XV4814 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1672,16 +1786,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1721,15 +1838,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1758,7 +1890,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1787,7 +1922,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1804,16 +1942,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1826,7 +1967,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-PIC4825A, 27-PIC4825A, 27-PIC4825B, 27-PIC4825B, 27-PIC4825C, 27-PIC4825C, 27-PT4825, 27-PT4825</t>
+          <t>Members: 27-PIC4825A, 27-PIC4825B, 27-PIC4825C, 27-PT4825</t>
         </is>
       </c>
     </row>
@@ -1853,15 +1994,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1890,7 +2046,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1919,7 +2078,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1936,16 +2098,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1958,7 +2123,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-HS4826, 27-XV4826, 27-XV4826, 27-XY4826, 27-ZL4826, 27-ZS4826</t>
+          <t>Members: 27-HS4826, 27-XV4826, 27-XY4826, 27-ZL4826, 27-ZS4826</t>
         </is>
       </c>
     </row>
@@ -1985,15 +2150,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2017,12 +2197,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>27-XV4826</t>
+          <t>27-XV4826 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2046,12 +2229,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>27-XV4826</t>
+          <t>27-XV4826 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2075,12 +2261,15 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>27-XV4826</t>
+          <t>27-XV4826 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2104,12 +2293,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>27-XV4826</t>
+          <t>27-XV4826 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2126,16 +2318,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2148,7 +2343,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-HS4828, 27-XV4828, 27-XV4828, 27-XY4828, 27-ZL4828, 27-ZS4828</t>
+          <t>Members: 27-HS4828, 27-XV4828, 27-XY4828, 27-ZL4828, 27-ZS4828</t>
         </is>
       </c>
     </row>
@@ -2175,15 +2370,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2207,12 +2417,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>27-XV4828</t>
+          <t>27-XV4828 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2236,12 +2449,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>27-XV4828</t>
+          <t>27-XV4828 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2265,12 +2481,15 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>27-XV4828</t>
+          <t>27-XV4828 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2294,12 +2513,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>27-XV4828</t>
+          <t>27-XV4828 (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2316,16 +2538,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2338,7 +2563,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-PT4250A, 27-PT4250A, 27-PT4250B, 27-PT4250B</t>
+          <t>Members: 27-PT4250A, 27-PT4250B</t>
         </is>
       </c>
     </row>
@@ -2365,15 +2590,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2402,7 +2642,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2431,7 +2674,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2448,16 +2694,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2497,15 +2746,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2534,7 +2798,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2563,7 +2830,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2580,16 +2850,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2629,15 +2902,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2666,7 +2954,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2695,7 +2986,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2724,7 +3018,10 @@
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2753,7 +3050,10 @@
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2770,16 +3070,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2792,7 +3095,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-PIC4803, 27-PT4803, 27-PT4803, 27-PV4803, 27-PY4803</t>
+          <t>Members: 27-PIC4803, 27-PT4803, 27-PV4803, 27-PY4803</t>
         </is>
       </c>
     </row>
@@ -2819,15 +3122,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2856,7 +3174,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2885,7 +3206,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2902,16 +3226,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2924,7 +3251,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-PI4804, 27-PT4804, 27-PT4804</t>
+          <t>Members: 27-PI4804, 27-PT4804</t>
         </is>
       </c>
     </row>
@@ -2951,15 +3278,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2988,7 +3330,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3017,7 +3362,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3034,16 +3382,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3056,7 +3407,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-PI4805, 27-PT4805, 27-PT4805</t>
+          <t>Members: 27-PI4805, 27-PT4805</t>
         </is>
       </c>
     </row>
@@ -3083,15 +3434,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3120,7 +3486,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3149,7 +3518,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3166,16 +3538,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3188,7 +3563,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Members: 27-TI4806, 27-TT4806, 27-TT4806</t>
+          <t>Members: 27-TI4806, 27-TT4806</t>
         </is>
       </c>
     </row>
@@ -3215,15 +3590,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3252,7 +3642,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3281,7 +3674,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3298,16 +3694,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3347,15 +3746,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3384,7 +3798,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3413,7 +3830,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
